--- a/EDRMS_Records_and_Archive_Holdings_2026-08-24.xlsx
+++ b/EDRMS_Records_and_Archive_Holdings_2026-08-24.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Overview (s67)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Storage (s68)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Retrieval (s69)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Month and dept cuts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pending and disposal" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Reconciliation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Open items" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview (s67)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage (s68)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retrieval (s69)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Month and dept cuts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending and disposal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open items" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Total number of requestors (departments)</t>
+          <t>Total number of requestors (departments) (year, month)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Total number of requestors (RMs)</t>
+          <t>Total number of requestors (RMs) (year, month)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Total number of boxes stored</t>
+          <t>Total number of boxes stored (year, month)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Total number of folders stored</t>
+          <t>Total number of folders stored (year, month)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1992,17 +1992,17 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Total number of requestors (departments and RMs)</t>
+          <t>Total number of requestors (departments / RMs) (year, month)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Total number of boxes retrieved</t>
+          <t>Total number of boxes retrieved (year, month)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Total number of folders retrieved</t>
+          <t>Total number of folders retrieved (year, month)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Status, as printed</t>
+          <t>Status (Loan, Return to owner, For Disposal), as printed</t>
         </is>
       </c>
     </row>
